--- a/Analysis/04_Robust_Core_and_Policy/7_normative_policy_scenarios.xlsx
+++ b/Analysis/04_Robust_Core_and_Policy/7_normative_policy_scenarios.xlsx
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3483870967741935</v>
+        <v>0.3451612903225807</v>
       </c>
       <c r="D3" t="n">
         <v>54</v>
@@ -637,7 +637,7 @@
         <v>0.2967741935483871</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.4645161290322581</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.8677419354838709</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.3612903225806452</v>
+        <v>0.3580645161290323</v>
       </c>
       <c r="D8" t="n">
         <v>53</v>
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.4806451612903226</v>
+        <v>0.4903225806451613</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.4</v>
+        <v>0.3935483870967742</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -802,10 +802,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.5903225806451613</v>
+        <v>0.5967741935483871</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3129032258064516</v>
+        <v>0.3032258064516129</v>
       </c>
       <c r="D13" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4870967741935485</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4419354838709678</v>
+        <v>0.4451612903225807</v>
       </c>
       <c r="D15" t="n">
         <v>39</v>
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.5677419354838711</v>
+        <v>0.5483870967741936</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.3903225806451612</v>
+        <v>0.3806451612903226</v>
       </c>
       <c r="D17" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.3064516129032259</v>
+        <v>0.2967741935483871</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.5580645161290323</v>
+        <v>0.5451612903225806</v>
       </c>
       <c r="D19" t="n">
         <v>21</v>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.3806451612903226</v>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.6838709677419355</v>
+        <v>0.6806451612903226</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.3741935483870968</v>
+        <v>0.3709677419354839</v>
       </c>
       <c r="D22" t="n">
         <v>52</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.6516129032258065</v>
+        <v>0.6451612903225807</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.4129032258064517</v>
+        <v>0.4</v>
       </c>
       <c r="D24" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -1078,7 +1078,7 @@
         <v>0.5451612903225806</v>
       </c>
       <c r="D25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.3129032258064516</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="D26" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.3806451612903226</v>
+        <v>0.3903225806451613</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.4967741935483871</v>
+        <v>0.4774193548387097</v>
       </c>
       <c r="D28" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.6</v>
+        <v>0.6064516129032258</v>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9419354838709677</v>
+        <v>0.9483870967741936</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.7193548387096775</v>
       </c>
       <c r="D32" t="n">
         <v>9</v>
@@ -1246,7 +1246,7 @@
         <v>0.464516129032258</v>
       </c>
       <c r="D33" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.738709677419355</v>
+        <v>0.7451612903225807</v>
       </c>
       <c r="D34" t="n">
         <v>8</v>
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.6161290322580646</v>
+        <v>0.6967741935483871</v>
       </c>
       <c r="D35" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.4709677419354839</v>
+        <v>0.4612903225806452</v>
       </c>
       <c r="D36" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.832258064516129</v>
+        <v>0.8290322580645162</v>
       </c>
       <c r="D37" t="n">
         <v>5</v>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.3741935483870968</v>
+        <v>0.3903225806451613</v>
       </c>
       <c r="D38" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.4516129032258065</v>
+        <v>0.467741935483871</v>
       </c>
       <c r="D39" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.4709677419354839</v>
+        <v>0.4612903225806452</v>
       </c>
       <c r="D40" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.4258064516129033</v>
       </c>
       <c r="D41" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.6032258064516129</v>
+        <v>0.6064516129032258</v>
       </c>
       <c r="D42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.6064516129032258</v>
       </c>
       <c r="D43" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.4580645161290323</v>
+        <v>0.4645161290322581</v>
       </c>
       <c r="D44" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.8290322580645162</v>
+        <v>0.7806451612903227</v>
       </c>
       <c r="D45" t="n">
         <v>6</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.467741935483871</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="D46" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.3806451612903226</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="D47" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.267741935483871</v>
+        <v>0.2645161290322581</v>
       </c>
       <c r="D48" t="n">
         <v>61</v>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.4451612903225807</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="D49" t="n">
         <v>38</v>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.4258064516129033</v>
       </c>
       <c r="D50" t="n">
         <v>42</v>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.4935483870967742</v>
+        <v>0.5161290322580646</v>
       </c>
       <c r="D51" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
@@ -1666,7 +1666,7 @@
         <v>0.6258064516129032</v>
       </c>
       <c r="D53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.4903225806451613</v>
+        <v>0.4935483870967742</v>
       </c>
       <c r="D54" t="n">
         <v>26</v>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.5967741935483871</v>
+        <v>0.5612903225806453</v>
       </c>
       <c r="D55" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.4967741935483871</v>
+        <v>0.5</v>
       </c>
       <c r="D56" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.4645161290322581</v>
+        <v>0.4548387096774194</v>
       </c>
       <c r="D57" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.3193548387096774</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="D58" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.6064516129032258</v>
+        <v>0.5967741935483871</v>
       </c>
       <c r="D59" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.4387096774193548</v>
+        <v>0.435483870967742</v>
       </c>
       <c r="D60" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.4</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="D61" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.3225806451612904</v>
+        <v>0.3193548387096774</v>
       </c>
       <c r="D62" t="n">
         <v>55</v>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.4419354838709677</v>
+        <v>0.4290322580645162</v>
       </c>
       <c r="D63" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
@@ -1897,7 +1897,7 @@
         <v>0.8233870967741935</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E64" t="b">
         <v>1</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.3112903225806452</v>
+        <v>0.3088709677419355</v>
       </c>
       <c r="D65" t="n">
         <v>53</v>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.5330645161290323</v>
+        <v>0.5596774193548387</v>
       </c>
       <c r="D67" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.8588709677419355</v>
+        <v>0.8564516129032258</v>
       </c>
       <c r="D68" t="n">
         <v>3</v>
@@ -2002,7 +2002,7 @@
         <v>0.7346774193548387</v>
       </c>
       <c r="D69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E69" t="b">
         <v>1</v>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.3637096774193548</v>
+        <v>0.3612903225806451</v>
       </c>
       <c r="D70" t="n">
         <v>49</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.4693548387096774</v>
+        <v>0.4766129032258065</v>
       </c>
       <c r="D71" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
@@ -2062,10 +2062,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.35</v>
       </c>
       <c r="D72" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.6040322580645161</v>
+        <v>0.6088709677419355</v>
       </c>
       <c r="D74" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.2830645161290323</v>
+        <v>0.2758064516129032</v>
       </c>
       <c r="D75" t="n">
         <v>56</v>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.5387096774193549</v>
+        <v>0.5362903225806452</v>
       </c>
       <c r="D76" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.5379032258064517</v>
+        <v>0.5403225806451613</v>
       </c>
       <c r="D77" t="n">
         <v>27</v>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.6362903225806452</v>
+        <v>0.621774193548387</v>
       </c>
       <c r="D78" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.4887096774193548</v>
+        <v>0.4814516129032258</v>
       </c>
       <c r="D79" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.3040322580645161</v>
+        <v>0.2967741935483871</v>
       </c>
       <c r="D80" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.5701612903225806</v>
+        <v>0.5604838709677419</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.4443548387096774</v>
+        <v>0.4274193548387096</v>
       </c>
       <c r="D82" t="n">
         <v>36</v>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.6669354838709678</v>
+        <v>0.6645161290322581</v>
       </c>
       <c r="D83" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.3685483870967742</v>
+        <v>0.3661290322580645</v>
       </c>
       <c r="D84" t="n">
         <v>47</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.6088709677419355</v>
+        <v>0.6040322580645161</v>
       </c>
       <c r="D85" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.4161290322580645</v>
+        <v>0.4064516129032258</v>
       </c>
       <c r="D86" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
@@ -2380,7 +2380,7 @@
         <v>0.6677419354838711</v>
       </c>
       <c r="D87" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.2411290322580645</v>
+        <v>0.2362903225806451</v>
       </c>
       <c r="D88" t="n">
         <v>57</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.4169354838709678</v>
+        <v>0.4241935483870968</v>
       </c>
       <c r="D89" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.6387096774193548</v>
+        <v>0.6241935483870967</v>
       </c>
       <c r="D90" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.6314516129032258</v>
+        <v>0.6362903225806452</v>
       </c>
       <c r="D91" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.9516129032258064</v>
+        <v>0.9564516129032258</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.7709677419354839</v>
+        <v>0.778225806451613</v>
       </c>
       <c r="D94" t="n">
         <v>7</v>
@@ -2548,7 +2548,7 @@
         <v>0.4088709677419354</v>
       </c>
       <c r="D95" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.6733870967741935</v>
+        <v>0.6782258064516129</v>
       </c>
       <c r="D96" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.6879032258064517</v>
+        <v>0.7483870967741936</v>
       </c>
       <c r="D97" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E97" t="b">
         <v>1</v>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>0.4169354838709678</v>
+        <v>0.4096774193548387</v>
       </c>
       <c r="D98" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0.8185483870967742</v>
+        <v>0.8161290322580645</v>
       </c>
       <c r="D99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E99" t="b">
         <v>1</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0.285483870967742</v>
+        <v>0.2975806451612903</v>
       </c>
       <c r="D100" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0.3887096774193549</v>
+        <v>0.4008064516129032</v>
       </c>
       <c r="D101" t="n">
         <v>44</v>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0.4217741935483871</v>
+        <v>0.4145161290322581</v>
       </c>
       <c r="D102" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.4758064516129032</v>
+        <v>0.492741935483871</v>
       </c>
       <c r="D103" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.6903225806451613</v>
+        <v>0.692741935483871</v>
       </c>
       <c r="D104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E104" t="b">
         <v>1</v>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0.5790322580645162</v>
+        <v>0.5983870967741935</v>
       </c>
       <c r="D105" t="n">
         <v>20</v>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.3782258064516129</v>
+        <v>0.3830645161290323</v>
       </c>
       <c r="D106" t="n">
         <v>45</v>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0.8516129032258065</v>
+        <v>0.8153225806451613</v>
       </c>
       <c r="D107" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E107" t="b">
         <v>1</v>
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.5225806451612903</v>
+        <v>0.5346774193548387</v>
       </c>
       <c r="D108" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.4201612903225806</v>
+        <v>0.425</v>
       </c>
       <c r="D109" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.1862903225806452</v>
+        <v>0.1838709677419355</v>
       </c>
       <c r="D110" t="n">
         <v>62</v>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0.4209677419354839</v>
+        <v>0.4258064516129032</v>
       </c>
       <c r="D111" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.3653225806451613</v>
+        <v>0.3701612903225807</v>
       </c>
       <c r="D112" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.467741935483871</v>
+        <v>0.4846774193548387</v>
       </c>
       <c r="D113" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
@@ -2947,7 +2947,7 @@
         <v>0.2346774193548387</v>
       </c>
       <c r="D114" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>0.5669354838709677</v>
       </c>
       <c r="D115" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0.571774193548387</v>
+        <v>0.5741935483870967</v>
       </c>
       <c r="D116" t="n">
         <v>21</v>
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>0.6879032258064516</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="D117" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>0.5620967741935483</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="D118" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.5266129032258065</v>
+        <v>0.5193548387096774</v>
       </c>
       <c r="D119" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0.2298387096774194</v>
+        <v>0.2201612903225806</v>
       </c>
       <c r="D120" t="n">
         <v>60</v>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>0.5588709677419355</v>
+        <v>0.5516129032258065</v>
       </c>
       <c r="D121" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>0.3540322580645162</v>
+        <v>0.3516129032258065</v>
       </c>
       <c r="D122" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0.339516129032258</v>
+        <v>0.3298387096774194</v>
       </c>
       <c r="D123" t="n">
         <v>52</v>
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>0.2370967741935484</v>
+        <v>0.2346774193548387</v>
       </c>
       <c r="D124" t="n">
         <v>58</v>
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0.3741935483870968</v>
+        <v>0.3645161290322581</v>
       </c>
       <c r="D125" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0.8677419354838709</v>
       </c>
       <c r="D126" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E126" t="b">
         <v>1</v>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0.3887096774193548</v>
+        <v>0.3862903225806451</v>
       </c>
       <c r="D127" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
@@ -3241,7 +3241,7 @@
         <v>0.3411290322580645</v>
       </c>
       <c r="D128" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0.4137096774193548</v>
+        <v>0.4403225806451613</v>
       </c>
       <c r="D129" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>0.8887096774193548</v>
+        <v>0.8862903225806451</v>
       </c>
       <c r="D130" t="n">
         <v>3</v>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.3524193548387097</v>
       </c>
       <c r="D132" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0.4806451612903225</v>
+        <v>0.4879032258064515</v>
       </c>
       <c r="D133" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0.4104838709677419</v>
+        <v>0.4056451612903226</v>
       </c>
       <c r="D134" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0.4629032258064516</v>
       </c>
       <c r="D135" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0.5411290322580645</v>
+        <v>0.5459677419354839</v>
       </c>
       <c r="D136" t="n">
         <v>18</v>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0.3733870967741936</v>
+        <v>0.3661290322580645</v>
       </c>
       <c r="D137" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>0.4540322580645161</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="D138" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E138" t="b">
         <v>0</v>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0.3798387096774193</v>
+        <v>0.382258064516129</v>
       </c>
       <c r="D139" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>0.4661290322580645</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="D140" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>0.3354838709677419</v>
+        <v>0.3282258064516129</v>
       </c>
       <c r="D141" t="n">
         <v>60</v>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.3483870967741935</v>
+        <v>0.3411290322580645</v>
       </c>
       <c r="D142" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.5306451612903226</v>
+        <v>0.5209677419354839</v>
       </c>
       <c r="D143" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.3379032258064516</v>
       </c>
       <c r="D144" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0.7104838709677419</v>
+        <v>0.7080645161290322</v>
       </c>
       <c r="D145" t="n">
         <v>10</v>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0.3540322580645161</v>
+        <v>0.3516129032258064</v>
       </c>
       <c r="D146" t="n">
         <v>56</v>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0.7008064516129032</v>
+        <v>0.6959677419354838</v>
       </c>
       <c r="D147" t="n">
         <v>11</v>
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>0.3927419354838709</v>
+        <v>0.3830645161290323</v>
       </c>
       <c r="D148" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
@@ -3682,7 +3682,7 @@
         <v>0.460483870967742</v>
       </c>
       <c r="D149" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>0.3669354838709677</v>
+        <v>0.3620967741935484</v>
       </c>
       <c r="D150" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>0.3508064516129032</v>
+        <v>0.3580645161290323</v>
       </c>
       <c r="D151" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>0.4008064516129032</v>
+        <v>0.3862903225806451</v>
       </c>
       <c r="D152" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>0.6612903225806451</v>
+        <v>0.6661290322580644</v>
       </c>
       <c r="D153" t="n">
         <v>13</v>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>0.9306451612903226</v>
+        <v>0.935483870967742</v>
       </c>
       <c r="D154" t="n">
         <v>1</v>
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>0.7451612903225806</v>
+        <v>0.7524193548387097</v>
       </c>
       <c r="D156" t="n">
         <v>9</v>
@@ -3850,7 +3850,7 @@
         <v>0.4475806451612904</v>
       </c>
       <c r="D157" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>0.7596774193548387</v>
+        <v>0.7645161290322581</v>
       </c>
       <c r="D158" t="n">
         <v>8</v>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>0.5451612903225806</v>
+        <v>0.6056451612903225</v>
       </c>
       <c r="D159" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>0.4975806451612903</v>
+        <v>0.4903225806451613</v>
       </c>
       <c r="D160" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>0.8669354838709677</v>
+        <v>0.8645161290322581</v>
       </c>
       <c r="D161" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E161" t="b">
         <v>1</v>
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>0.4104838709677419</v>
+        <v>0.4225806451612903</v>
       </c>
       <c r="D162" t="n">
         <v>41</v>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>0.4661290322580646</v>
+        <v>0.4782258064516129</v>
       </c>
       <c r="D163" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>0.5290322580645161</v>
+        <v>0.5217741935483871</v>
       </c>
       <c r="D164" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>0.3548387096774193</v>
+        <v>0.3717741935483871</v>
       </c>
       <c r="D165" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>0.5693548387096774</v>
+        <v>0.5717741935483871</v>
       </c>
       <c r="D166" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>0.564516129032258</v>
+        <v>0.5838709677419355</v>
       </c>
       <c r="D167" t="n">
         <v>16</v>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0.4870967741935484</v>
+        <v>0.4919354838709677</v>
       </c>
       <c r="D168" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.8346774193548387</v>
       </c>
       <c r="D169" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E169" t="b">
         <v>1</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>0.4395161290322581</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="D170" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>0.3564516129032258</v>
+        <v>0.3612903225806452</v>
       </c>
       <c r="D171" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>0.3217741935483871</v>
+        <v>0.3193548387096774</v>
       </c>
       <c r="D172" t="n">
         <v>61</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>0.4314516129032258</v>
+        <v>0.4362903225806452</v>
       </c>
       <c r="D173" t="n">
         <v>39</v>
@@ -4204,7 +4204,7 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>0.432258064516129</v>
+        <v>0.4370967741935484</v>
       </c>
       <c r="D174" t="n">
         <v>38</v>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>0.475</v>
+        <v>0.4919354838709677</v>
       </c>
       <c r="D175" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>0.4362903225806452</v>
+        <v>0.4387096774193548</v>
       </c>
       <c r="D178" t="n">
         <v>37</v>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>0.4895161290322581</v>
+        <v>0.4629032258064516</v>
       </c>
       <c r="D179" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>0.4370967741935484</v>
+        <v>0.4395161290322581</v>
       </c>
       <c r="D180" t="n">
         <v>36</v>
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>0.3911290322580645</v>
+        <v>0.3838709677419355</v>
       </c>
       <c r="D181" t="n">
         <v>46</v>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.3774193548387097</v>
       </c>
       <c r="D182" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>0.6790322580645161</v>
+        <v>0.671774193548387</v>
       </c>
       <c r="D183" t="n">
         <v>12</v>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0.4870967741935484</v>
+        <v>0.4846774193548387</v>
       </c>
       <c r="D184" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>0.4419354838709677</v>
+        <v>0.432258064516129</v>
       </c>
       <c r="D185" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>0.3951612903225806</v>
+        <v>0.3927419354838709</v>
       </c>
       <c r="D186" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>0.5153225806451612</v>
+        <v>0.5056451612903226</v>
       </c>
       <c r="D187" t="n">
         <v>21</v>
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>0.3225806451612904</v>
+        <v>0.3193548387096774</v>
       </c>
       <c r="D189" t="n">
         <v>54</v>
@@ -4543,7 +4543,7 @@
         <v>0.2451612903225807</v>
       </c>
       <c r="D190" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>0.5153225806451613</v>
+        <v>0.5508064516129033</v>
       </c>
       <c r="D191" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
@@ -4582,7 +4582,7 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0.8225806451612904</v>
+        <v>0.8193548387096774</v>
       </c>
       <c r="D192" t="n">
         <v>3</v>
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>0.4153225806451613</v>
+        <v>0.4120967741935484</v>
       </c>
       <c r="D194" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>0.5185483870967741</v>
+        <v>0.5282258064516129</v>
       </c>
       <c r="D195" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>0.4975806451612904</v>
+        <v>0.4911290322580646</v>
       </c>
       <c r="D196" t="n">
         <v>34</v>
@@ -4690,7 +4690,7 @@
         <v>0.457258064516129</v>
       </c>
       <c r="D197" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>0.6008064516129031</v>
+        <v>0.6072580645161291</v>
       </c>
       <c r="D198" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>0.2403225806451613</v>
+        <v>0.2306451612903226</v>
       </c>
       <c r="D199" t="n">
         <v>60</v>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>0.5217741935483871</v>
+        <v>0.5185483870967742</v>
       </c>
       <c r="D200" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0.5153225806451613</v>
+        <v>0.5185483870967742</v>
       </c>
       <c r="D201" t="n">
         <v>31</v>
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>0.6895161290322581</v>
+        <v>0.6701612903225808</v>
       </c>
       <c r="D202" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E202" t="b">
         <v>1</v>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>0.4048387096774193</v>
+        <v>0.3951612903225806</v>
       </c>
       <c r="D203" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E203" t="b">
         <v>0</v>
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>0.2451612903225807</v>
+        <v>0.2354838709677419</v>
       </c>
       <c r="D204" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E204" t="b">
         <v>0</v>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>0.5403225806451613</v>
+        <v>0.5274193548387096</v>
       </c>
       <c r="D205" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E205" t="b">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>0.3733870967741935</v>
+        <v>0.3508064516129032</v>
       </c>
       <c r="D206" t="n">
         <v>51</v>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>0.5782258064516129</v>
+        <v>0.575</v>
       </c>
       <c r="D207" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E207" t="b">
         <v>0</v>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>0.3435483870967742</v>
+        <v>0.3403225806451613</v>
       </c>
       <c r="D208" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E208" t="b">
         <v>0</v>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>0.5637096774193548</v>
+        <v>0.557258064516129</v>
       </c>
       <c r="D209" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E209" t="b">
         <v>0</v>
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>0.4532258064516129</v>
+        <v>0.4403225806451613</v>
       </c>
       <c r="D210" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E210" t="b">
         <v>0</v>
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>0.2911290322580645</v>
+        <v>0.2846774193548387</v>
       </c>
       <c r="D212" t="n">
         <v>55</v>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>0.4306451612903226</v>
+        <v>0.4403225806451613</v>
       </c>
       <c r="D213" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E213" t="b">
         <v>0</v>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0.5879032258064516</v>
+        <v>0.5685483870967741</v>
       </c>
       <c r="D214" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E214" t="b">
         <v>0</v>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>0.5064516129032258</v>
+        <v>0.5129032258064516</v>
       </c>
       <c r="D215" t="n">
         <v>33</v>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>0.9548387096774194</v>
+        <v>0.9612903225806452</v>
       </c>
       <c r="D216" t="n">
         <v>1</v>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>0.6685483870967742</v>
+        <v>0.6782258064516129</v>
       </c>
       <c r="D218" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E218" t="b">
         <v>1</v>
@@ -5152,7 +5152,7 @@
         <v>0.4717741935483871</v>
       </c>
       <c r="D219" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E219" t="b">
         <v>0</v>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>0.7717741935483871</v>
+        <v>0.7782258064516129</v>
       </c>
       <c r="D220" t="n">
         <v>5</v>
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>0.7040322580645162</v>
+        <v>0.7846774193548387</v>
       </c>
       <c r="D221" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E221" t="b">
         <v>1</v>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>0.553225806451613</v>
+        <v>0.5435483870967742</v>
       </c>
       <c r="D222" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E222" t="b">
         <v>0</v>
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>0.7241935483870967</v>
+        <v>0.7209677419354839</v>
       </c>
       <c r="D223" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E223" t="b">
         <v>1</v>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>0.3951612903225807</v>
+        <v>0.4112903225806452</v>
       </c>
       <c r="D224" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E224" t="b">
         <v>0</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>0.5258064516129033</v>
+        <v>0.5419354838709678</v>
       </c>
       <c r="D225" t="n">
         <v>27</v>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>0.4258064516129032</v>
+        <v>0.4161290322580645</v>
       </c>
       <c r="D226" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E226" t="b">
         <v>0</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>0.3967741935483871</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="D227" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E227" t="b">
         <v>0</v>
@@ -5338,7 +5338,7 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>0.6653225806451613</v>
+        <v>0.6685483870967742</v>
       </c>
       <c r="D228" t="n">
         <v>11</v>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>0.567741935483871</v>
+        <v>0.5935483870967742</v>
       </c>
       <c r="D229" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E229" t="b">
         <v>0</v>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>0.5596774193548387</v>
+        <v>0.5661290322580645</v>
       </c>
       <c r="D230" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E230" t="b">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>0.7935483870967742</v>
+        <v>0.7451612903225806</v>
       </c>
       <c r="D231" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E231" t="b">
         <v>1</v>
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>0.5193548387096775</v>
+        <v>0.535483870967742</v>
       </c>
       <c r="D232" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E232" t="b">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>0.4233870967741936</v>
+        <v>0.4298387096774194</v>
       </c>
       <c r="D233" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E233" t="b">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>0.2338709677419355</v>
+        <v>0.2306451612903226</v>
       </c>
       <c r="D234" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E234" t="b">
         <v>0</v>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>0.5790322580645162</v>
+        <v>0.585483870967742</v>
       </c>
       <c r="D235" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E235" t="b">
         <v>0</v>
@@ -5506,10 +5506,10 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>0.4685483870967742</v>
+        <v>0.475</v>
       </c>
       <c r="D236" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E236" t="b">
         <v>0</v>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>0.560483870967742</v>
+        <v>0.5830645161290324</v>
       </c>
       <c r="D237" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E237" t="b">
         <v>0</v>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>0.5830645161290322</v>
+        <v>0.5862903225806452</v>
       </c>
       <c r="D240" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E240" t="b">
         <v>0</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>0.6161290322580645</v>
+        <v>0.5806451612903225</v>
       </c>
       <c r="D241" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E241" t="b">
         <v>0</v>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>0.4104838709677419</v>
+        <v>0.4137096774193548</v>
       </c>
       <c r="D242" t="n">
         <v>46</v>
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>0.4338709677419355</v>
+        <v>0.4241935483870968</v>
       </c>
       <c r="D243" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E243" t="b">
         <v>0</v>
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>0.2548387096774193</v>
+        <v>0.2419354838709677</v>
       </c>
       <c r="D244" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E244" t="b">
         <v>0</v>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>0.4604838709677419</v>
+        <v>0.4508064516129032</v>
       </c>
       <c r="D245" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E245" t="b">
         <v>0</v>
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>0.4411290322580645</v>
+        <v>0.4379032258064516</v>
       </c>
       <c r="D246" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E246" t="b">
         <v>0</v>
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>0.3741935483870968</v>
+        <v>0.3612903225806452</v>
       </c>
       <c r="D247" t="n">
         <v>50</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>0.2806451612903226</v>
+        <v>0.2774193548387097</v>
       </c>
       <c r="D248" t="n">
         <v>56</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>0.3475806451612903</v>
+        <v>0.3346774193548387</v>
       </c>
       <c r="D249" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E249" t="b">
         <v>0</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9419354838709677</v>
+        <v>0.9483870967741936</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.8677419354838709</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -5925,7 +5925,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.832258064516129</v>
+        <v>0.8290322580645162</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8290322580645162</v>
+        <v>0.7806451612903227</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.738709677419355</v>
+        <v>0.7451612903225807</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.7193548387096775</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -6026,11 +6026,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sec20</t>
+          <t>sec34</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6838709677419355</v>
+        <v>0.6967741935483871</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9516129032258064</v>
+        <v>0.9564516129032258</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8588709677419355</v>
+        <v>0.8564516129032258</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -6110,11 +6110,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sec44</t>
+          <t>sec1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8516129032258065</v>
+        <v>0.8233870967741935</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -6131,11 +6131,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sec1</t>
+          <t>sec36</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8233870967741935</v>
+        <v>0.8161290322580645</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -6152,11 +6152,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sec36</t>
+          <t>sec44</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.8185483870967742</v>
+        <v>0.8153225806451613</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.7709677419354839</v>
+        <v>0.778225806451613</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
@@ -6194,11 +6194,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sec6</t>
+          <t>sec34</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.7346774193548387</v>
+        <v>0.7483870967741936</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -6215,11 +6215,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sec41</t>
+          <t>sec6</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6903225806451613</v>
+        <v>0.7346774193548387</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
@@ -6236,11 +6236,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sec34</t>
+          <t>sec41</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.6879032258064517</v>
+        <v>0.692741935483871</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9548387096774194</v>
+        <v>0.9612903225806452</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.8225806451612904</v>
+        <v>0.8193548387096774</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -6320,11 +6320,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sec44</t>
+          <t>sec34</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7935483870967742</v>
+        <v>0.7846774193548387</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -6345,7 +6345,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.7717741935483871</v>
+        <v>0.7782258064516129</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -6362,11 +6362,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sec36</t>
+          <t>sec44</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7241935483870967</v>
+        <v>0.7451612903225806</v>
       </c>
       <c r="D27" t="n">
         <v>6</v>
@@ -6383,11 +6383,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sec34</t>
+          <t>sec36</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.7040322580645162</v>
+        <v>0.7209677419354839</v>
       </c>
       <c r="D28" t="n">
         <v>7</v>
@@ -6425,11 +6425,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sec15</t>
+          <t>sec31</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.6895161290322581</v>
+        <v>0.6782258064516129</v>
       </c>
       <c r="D30" t="n">
         <v>9</v>
@@ -6446,11 +6446,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sec31</t>
+          <t>sec15</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.6685483870967742</v>
+        <v>0.6701612903225808</v>
       </c>
       <c r="D31" t="n">
         <v>10</v>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9306451612903226</v>
+        <v>0.935483870967742</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.8887096774193548</v>
+        <v>0.8862903225806451</v>
       </c>
       <c r="D34" t="n">
         <v>3</v>
@@ -6530,11 +6530,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sec44</t>
+          <t>sec1</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.8677419354838709</v>
       </c>
       <c r="D35" t="n">
         <v>4</v>
@@ -6551,11 +6551,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>sec1</t>
+          <t>sec36</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.8677419354838709</v>
+        <v>0.8645161290322581</v>
       </c>
       <c r="D36" t="n">
         <v>5</v>
@@ -6572,11 +6572,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>sec36</t>
+          <t>sec44</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.8669354838709677</v>
+        <v>0.8346774193548387</v>
       </c>
       <c r="D37" t="n">
         <v>6</v>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.7596774193548387</v>
+        <v>0.7645161290322581</v>
       </c>
       <c r="D39" t="n">
         <v>8</v>
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.7451612903225806</v>
+        <v>0.7524193548387097</v>
       </c>
       <c r="D40" t="n">
         <v>9</v>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.7104838709677419</v>
+        <v>0.7080645161290322</v>
       </c>
       <c r="D41" t="n">
         <v>10</v>
@@ -6765,7 +6765,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7552</v>
+        <v>0.8013</v>
       </c>
       <c r="J2" t="n">
         <v>10000</v>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9879</v>
+        <v>0.9877</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0015</v>
+        <v>0.0005</v>
       </c>
       <c r="J4" t="n">
         <v>10000</v>
@@ -6853,13 +6853,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9077</v>
+        <v>0.9084</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0063</v>
+        <v>0.0051</v>
       </c>
       <c r="J5" t="n">
         <v>10000</v>
@@ -6882,34 +6882,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sec44</t>
+          <t>sec1</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.1354166666666667</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Robust Core</t>
+          <t>Not Robust Core</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8998</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0776</v>
+        <v>0.1361</v>
       </c>
       <c r="J6" t="n">
         <v>10000</v>
@@ -6918,34 +6918,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sec1</t>
+          <t>sec44</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Not Robust Core</t>
+          <t>Robust Core</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8641</v>
+        <v>0.781</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1588</v>
+        <v>0.0565</v>
       </c>
       <c r="J7" t="n">
         <v>10000</v>
@@ -6961,13 +6961,13 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
         <v>0.1875</v>
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.5906</v>
+        <v>0.6079</v>
       </c>
       <c r="I8" t="n">
         <v>0.0005</v>
@@ -6997,7 +6997,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.7398</v>
+        <v>0.7333</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -7033,13 +7033,13 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.6797</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -7062,20 +7062,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sec20</t>
+          <t>sec34</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>13.5</v>
+        <v>9.25</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -7086,7 +7086,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.4497</v>
+        <v>0.5475</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -7098,20 +7098,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sec34</t>
+          <t>sec20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>11.75</v>
+        <v>13.75</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.2398</v>
+        <v>0.4194</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -7141,13 +7141,13 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.271</v>
+        <v>0.2672</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7177,13 +7177,13 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7194,7 +7194,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.1317</v>
+        <v>0.1022</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -7206,20 +7206,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sec54</t>
+          <t>sec52</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.5</v>
+        <v>15.25</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.2029</v>
+        <v>0.1634</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -7242,20 +7242,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sec22</t>
+          <t>sec28</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.5</v>
+        <v>18.75</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.1793</v>
+        <v>0.1628</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -7285,13 +7285,13 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>19.75</v>
+        <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.1637</v>
+        <v>0.1607</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -7314,20 +7314,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sec52</t>
+          <t>sec22</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.25</v>
+        <v>16.5</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -7338,7 +7338,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.163</v>
+        <v>0.138</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -7350,20 +7350,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sec28</t>
+          <t>sec58</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.75</v>
+        <v>23.25</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -7374,7 +7374,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.1585</v>
+        <v>0.1021</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -7386,20 +7386,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sec58</t>
+          <t>sec11</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.1166</v>
+        <v>0.0849</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -7429,13 +7429,13 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>24.5</v>
+        <v>28</v>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E21" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.0737</v>
+        <v>0.0583</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>10000</v>
@@ -7458,20 +7458,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sec43</t>
+          <t>sec54</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>32</v>
+        <v>20.25</v>
       </c>
       <c r="D22" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -7482,7 +7482,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.0399</v>
+        <v>0.0541</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -7494,23 +7494,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sec48</t>
+          <t>sec43</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>33.5</v>
+        <v>30.75</v>
       </c>
       <c r="D23" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.0379</v>
+        <v>0.0413</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -7530,23 +7530,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sec11</t>
+          <t>sec48</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>17.75</v>
+        <v>33</v>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.0359</v>
+        <v>0.0405</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -7573,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>32.25</v>
+        <v>32.5</v>
       </c>
       <c r="D25" t="n">
         <v>23</v>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.0319</v>
+        <v>0.0396</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -7602,20 +7602,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sec56</t>
+          <t>sec42</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>37.25</v>
+        <v>16.5</v>
       </c>
       <c r="D26" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E26" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.016</v>
+        <v>0.0175</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -7638,20 +7638,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sec32</t>
+          <t>sec53</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>36.25</v>
+        <v>25.25</v>
       </c>
       <c r="D27" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E27" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -7662,7 +7662,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.0159</v>
+        <v>0.0135</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -7674,20 +7674,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sec53</t>
+          <t>sec32</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>25.5</v>
+        <v>36.25</v>
       </c>
       <c r="D28" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E28" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.0128</v>
+        <v>0.0125</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -7717,13 +7717,13 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>29</v>
+        <v>31.25</v>
       </c>
       <c r="D29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E29" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0072</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -7746,20 +7746,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sec10</t>
+          <t>sec56</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>34.75</v>
+        <v>38.75</v>
       </c>
       <c r="D30" t="n">
         <v>30</v>
       </c>
       <c r="E30" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -7782,20 +7782,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sec12</t>
+          <t>sec50</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>55.75</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.0035</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -7818,20 +7818,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sec13</t>
+          <t>sec38</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>28.25</v>
+        <v>32.25</v>
       </c>
       <c r="D32" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E32" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -7854,20 +7854,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sec14</t>
+          <t>sec10</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>36.5</v>
+        <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E33" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -7890,17 +7890,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sec16</t>
+          <t>sec12</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>46.5</v>
+        <v>56.25</v>
       </c>
       <c r="D34" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="E34" t="n">
         <v>60</v>
@@ -7926,20 +7926,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sec17</t>
+          <t>sec13</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>57.25</v>
+        <v>29.5</v>
       </c>
       <c r="D35" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="E35" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -7962,20 +7962,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>sec18</t>
+          <t>sec14</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>22</v>
+        <v>36.25</v>
       </c>
       <c r="D36" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E36" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -7998,20 +7998,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sec19</t>
+          <t>sec16</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>46</v>
+        <v>48.25</v>
       </c>
       <c r="D37" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -8034,20 +8034,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sec2</t>
+          <t>sec17</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>52</v>
+        <v>57.5</v>
       </c>
       <c r="D38" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E38" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -8070,20 +8070,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sec21</t>
+          <t>sec18</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>52</v>
+        <v>23.75</v>
       </c>
       <c r="D39" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="E39" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -8106,20 +8106,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>sec23</t>
+          <t>sec19</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>42.25</v>
+        <v>49</v>
       </c>
       <c r="D40" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E40" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -8142,20 +8142,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>sec25</t>
+          <t>sec2</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>55</v>
+        <v>51.25</v>
       </c>
       <c r="D41" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E41" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -8178,20 +8178,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sec26</t>
+          <t>sec21</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="D42" t="n">
         <v>47</v>
       </c>
-      <c r="D42" t="n">
-        <v>40</v>
-      </c>
       <c r="E42" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -8214,20 +8214,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sec3</t>
+          <t>sec23</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>59.5</v>
+        <v>43.5</v>
       </c>
       <c r="D43" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="E43" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -8250,20 +8250,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sec37</t>
+          <t>sec25</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D44" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E44" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -8286,20 +8286,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sec38</t>
+          <t>sec26</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>34</v>
+        <v>44.5</v>
       </c>
       <c r="D45" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E45" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -8322,20 +8322,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>sec39</t>
+          <t>sec3</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>32.5</v>
+        <v>58.75</v>
       </c>
       <c r="D46" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="E46" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -8358,20 +8358,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>sec4</t>
+          <t>sec37</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>32.75</v>
+        <v>47.25</v>
       </c>
       <c r="D47" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E47" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -8394,20 +8394,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>sec40</t>
+          <t>sec39</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>44.75</v>
+        <v>34.75</v>
       </c>
       <c r="D48" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E48" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -8430,20 +8430,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>sec42</t>
+          <t>sec4</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>19</v>
+        <v>27.25</v>
       </c>
       <c r="D49" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E49" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -8466,20 +8466,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>sec45</t>
+          <t>sec40</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>31.25</v>
+        <v>41.75</v>
       </c>
       <c r="D50" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E50" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -8502,20 +8502,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>sec46</t>
+          <t>sec45</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D51" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E51" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -8538,20 +8538,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>sec47</t>
+          <t>sec46</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>61.25</v>
+        <v>45.25</v>
       </c>
       <c r="D52" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="E52" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -8574,20 +8574,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>sec49</t>
+          <t>sec47</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="D53" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E53" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -8610,20 +8610,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sec50</t>
+          <t>sec49</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>27.25</v>
+        <v>40.25</v>
       </c>
       <c r="D54" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E54" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -8653,10 +8653,10 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>61.25</v>
+        <v>61</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E55" t="n">
         <v>62</v>
@@ -8689,10 +8689,10 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>55.25</v>
+        <v>56</v>
       </c>
       <c r="D56" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
         <v>60</v>
@@ -8725,13 +8725,13 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>39</v>
+        <v>39.25</v>
       </c>
       <c r="D57" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E57" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -8761,10 +8761,10 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>45.5</v>
+        <v>47.75</v>
       </c>
       <c r="D58" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E58" t="n">
         <v>52</v>
@@ -8797,10 +8797,10 @@
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>53.25</v>
+        <v>53</v>
       </c>
       <c r="D59" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E59" t="n">
         <v>58</v>
@@ -8833,13 +8833,13 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>39.75</v>
+        <v>40.75</v>
       </c>
       <c r="D60" t="n">
         <v>21</v>
       </c>
       <c r="E60" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -8869,13 +8869,13 @@
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D61" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -8905,13 +8905,13 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>29.25</v>
+        <v>28.75</v>
       </c>
       <c r="D62" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E62" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -8941,13 +8941,13 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>42.75</v>
+        <v>43</v>
       </c>
       <c r="D63" t="n">
         <v>34</v>
       </c>
       <c r="E63" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
